--- a/api/templates/pk_annual_utilization_rates/fr.xlsx
+++ b/api/templates/pk_annual_utilization_rates/fr.xlsx
@@ -1,32 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/pk_annual_utilization_rates/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5900711C-EB87-7C4A-AAEA-9F470B859205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500"/>
   </bookViews>
   <sheets>
-    <sheet name="National Utilization Rate" sheetId="1" r:id="rId1"/>
-    <sheet name="Provincial Utilization Rate" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="National Utilization Rate" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Provincial Utilization Rate" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+  <si>
+    <t>Tendances nationales des taux d’utilisation annuels</t>
+  </si>
   <si>
     <t>Dates: &lt;Dates&gt;</t>
   </si>
@@ -40,75 +32,75 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Dispositifs</t>
+  </si>
+  <si>
+    <t># Modules</t>
+  </si>
+  <si>
+    <t>Capacité quotidienne</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t># Modules</t>
+    <t>&lt;modules&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dailyCapacity&gt;</t>
+  </si>
+  <si>
+    <t>Provincial Trends in Annual Utilization Rates</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;</t>
   </si>
   <si>
     <t>Daily Capacity</t>
   </si>
   <si>
-    <t>&lt;dailyCapacity&gt;</t>
-  </si>
-  <si>
-    <t>&lt;modules&gt;</t>
-  </si>
-  <si>
-    <t>Provincial Trends in Annual Utilization Rates</t>
-  </si>
-  <si>
-    <t>&lt;StatesLabel&gt;</t>
-  </si>
-  <si>
     <t>&lt;stateName&gt;</t>
-  </si>
-  <si>
-    <t>Tendances nationales des taux d’utilisation annuels</t>
-  </si>
-  <si>
-    <t>Dispositifs</t>
-  </si>
-  <si>
-    <t>Capacité quotidienne</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -134,144 +126,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD7D7D7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -545,131 +430,141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="3" width="11" style="5"/>
+    <col min="2" max="3" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="3" width="11" style="5"/>
+    <col min="2" max="3" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/pk_annual_utilization_rates/fr.xlsx
+++ b/api/templates/pk_annual_utilization_rates/fr.xlsx
@@ -140,9 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>

--- a/api/templates/pk_annual_utilization_rates/fr.xlsx
+++ b/api/templates/pk_annual_utilization_rates/fr.xlsx
@@ -32,7 +32,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -140,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
